--- a/גאנט.xlsx
+++ b/גאנט.xlsx
@@ -531,12 +531,14 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -544,18 +546,21 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="7"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="5"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -29249,7 +29254,7 @@
   <dimension ref="A1:P47"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>51</v>
       </c>
@@ -29257,7 +29262,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>53</v>
       </c>
@@ -29265,7 +29270,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>55</v>
       </c>
@@ -29273,7 +29278,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>57</v>
       </c>
@@ -29284,7 +29289,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>60</v>
       </c>
@@ -29292,7 +29297,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>62</v>
       </c>
@@ -29300,7 +29305,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>64</v>
       </c>
@@ -29311,13 +29316,13 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="M8" s="5" t="s">
         <v>67</v>
       </c>
       <c r="N8" s="5"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>68</v>
       </c>
@@ -29326,7 +29331,7 @@
       </c>
       <c r="N9" s="5"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>70</v>
       </c>
@@ -29337,7 +29342,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>73</v>
       </c>
@@ -29345,11 +29350,11 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="5"/>
       <c r="M12" s="5"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>75</v>
       </c>
@@ -29358,32 +29363,32 @@
       </c>
       <c r="N13" s="5"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
         <v>77</v>
       </c>
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
         <v>78</v>
       </c>
       <c r="N15" s="5"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
         <v>79</v>
       </c>
       <c r="N16" s="5"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
         <v>80</v>
       </c>
       <c r="N17" s="5"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>81</v>
       </c>
@@ -29465,90 +29470,90 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="3"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
         <v>108</v>
       </c>
